--- a/docs/exports/day-2026-10-21.xlsx
+++ b/docs/exports/day-2026-10-21.xlsx
@@ -552,7 +552,7 @@
               <color rgb="0014322B"/>
               <sz val="13"/>
             </rPr>
-            <t xml:space="preserve">馬來西亞 AI 機房相關長約與交付節點仍須分開看待
+            <t xml:space="preserve">馬來西亞核准 27 件資料中心計畫、金額約 554 億美元
 </t>
           </r>
           <r>
@@ -561,12 +561,12 @@
               <color rgb="003B4A44"/>
               <sz val="11"/>
             </rPr>
-            <t>Bitdeer 在馬來西亞的 A201 規劃仍以 2027 年 1 月機房就緒、4 月全面上線為不同節點，而 Aolani 也只揭露最高 500 MW 的非約束性意向書。兩家案子都顯示 AI 機房以長約、機房進度與供電完成度各自衡量，不能把計畫性容量直接當成已部署容量。</t>
+            <t>10/21 檢視的區域報導指出，馬來西亞新增核准 27 件資料中心計畫，合計約 554 億美元。這組數字反映的是核准與投資承諾規模，不等同同日已完成接電、機櫃上架與商轉；對供應鏈而言，仍須看實際土建、變電與租戶導入節奏。</t>
           </r>
         </is>
       </c>
       <c r="C3" s="6" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
     </row>
     <row r="4" ht="66" customHeight="1">
@@ -584,7 +584,7 @@
               <color rgb="0014322B"/>
               <sz val="13"/>
             </rPr>
-            <t xml:space="preserve">神雲新廠與擴線計畫再度公開，產能時間表仍未一併定義
+            <t xml:space="preserve">馬來半島資料中心用電需求估 2030 年達 8,391MW，Johor 比重過半
 </t>
           </r>
           <r>
@@ -593,15 +593,15 @@
               <color rgb="003B4A44"/>
               <sz val="11"/>
             </rPr>
-            <t>神雲公布約 126.2 億元台灣投資案，涵蓋楊梅新廠、竹南與林口擴線，但公司未併同披露各站點的設備到位日期與開產驗收標準。這類案件仍以設備採購與擴產規劃為主，而非當前已出貨或已上線產能。</t>
+            <t>10/21 追蹤報導顯示，馬來半島資料中心在 2030 年的用電需求估達 8,391MW，且 Johor 占比超過一半。這是需求估算，不是現況負載；對供應鏈的實際影響仍取決於電力系統升級、並網審批與機房分期投運。</t>
           </r>
         </is>
       </c>
       <c r="C4" s="6" t="n">
-        <v>46314</v>
-      </c>
-    </row>
-    <row r="5" ht="66" customHeight="1">
+        <v>46316</v>
+      </c>
+    </row>
+    <row r="5" ht="82" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
           <t>03</t>
@@ -616,7 +616,7 @@
               <color rgb="0014322B"/>
               <sz val="13"/>
             </rPr>
-            <t xml:space="preserve">宸鴻與力成的封裝設備與玻璃基板驗證，仍以試產與客戶認證為核心
+            <t xml:space="preserve">越南電子製造擴產訊號升溫，十億美元級投資意向待落地
 </t>
           </r>
           <r>
@@ -625,12 +625,12 @@
               <color rgb="003B4A44"/>
               <sz val="11"/>
             </rPr>
-            <t>宸鴻提出兩年 60 億元 TGV 規劃，力成則披露近期設備採購與封裝驗證節點。這些動作都強調驗證、規模擴張與適配客戶流程，尚無法視為量產落地，因為設備採購、試產與客戶驗證是不同的節點。</t>
+            <t>10/21 匯整的供應鏈報導提到，越南電子與半導體測試鏈條持續出現十億美元等級投資意向，包括台系與韓系廠商的擴產規劃。現階段多為公告與媒體揭露，對產能與就業的實際影響仍須等正式核准、施工與設備進場時程。</t>
           </r>
         </is>
       </c>
       <c r="C5" s="9" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
     </row>
   </sheetData>
@@ -687,7 +687,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="178" customHeight="1">
+    <row r="3" ht="162" customHeight="1">
       <c r="A3" s="4" t="inlineStr">
         <is>
           <t>01</t>
@@ -702,7 +702,7 @@
               <color rgb="0014322B"/>
               <sz val="13"/>
             </rPr>
-            <t xml:space="preserve">馬來西亞 AI 機房相關長約與交付節點仍須分開看待
+            <t xml:space="preserve">馬來西亞核准 27 件資料中心計畫、金額約 554 億美元
 </t>
           </r>
           <r>
@@ -711,20 +711,20 @@
               <color rgb="003B4A44"/>
               <sz val="11"/>
             </rPr>
-            <t>Bitdeer 在馬來西亞的 A201 規劃仍以 2027 年 1 月機房就緒、4 月全面上線為不同節點，而 Aolani 也只揭露最高 500 MW 的非約束性意向書。兩家案子都顯示 AI 機房以長約、機房進度與供電完成度各自衡量，不能把計畫性容量直接當成已部署容量。AI 機房的關鍵節點涵蓋 GPU、伺服器機櫃、液冷和機房供電；公司更新中同時列出已上線 A101、規劃中 A201、集團 GPU 利用率和未來合約收入。這些數字屬不同層次：有的是當前已部署，另有的仍係規劃與長約。Bitdeer 披露 9 月 GPU 利用率 95%，但該值不能直接等同於 A201 的每月實際出力；A201 的階段交付仍分機房就緒與完整部署。Aolani 則列最高 500 MW 的非約束性 LOI，意思是未定義客戶最終落地與供電時間表。目前公開資料未完整說明 A201 交付條件、哪一批客戶已實際承租，以及機房通電與營收認列之間的落差。這些都仍須以正式交付公告、供電說明與長約條款為準。地點：馬來西亞柔佛州新山；A201、A101 兩處資料中心分別列示。</t>
+            <t>10/21 檢視的區域報導指出，馬來西亞新增核准 27 件資料中心計畫，合計約 554 億美元。這組數字反映的是核准與投資承諾規模，不等同同日已完成接電、機櫃上架與商轉；對供應鏈而言，仍須看實際土建、變電與租戶導入節奏。資料中心核准案會連動伺服器機櫃、配電、散熱、建廠與長週期電力設備需求。對台灣與東南亞鏈條的意義在於，新增核准會先轉化為工程與設備拉貨窗口，之後才是租戶實際裝機與營運收入。「27 件、554 億美元」是專案核准與總投資規模，不是可直接換算為當前上線 MW。若要評估短期影響，仍需拆開看土地取得、電力接入進度、機電建置與客戶簽約成熟度。公開報導未完整列出每件專案的通電日期、IT 負載與分期啟用節點，因此無法將核准總額直接換算為年度可用容量。地點：馬來西亞（以半島地區資料中心走廊為主，Johor 與吉隆坡周邊最受關注）。</t>
           </r>
         </is>
       </c>
       <c r="C3" s="6" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="D3" s="10" t="inlineStr">
         <is>
-          <t>對精密電源與量測設備業者而言，重點不是單一數字，而是機房是否能順利交付、通電與驗證。若客戶承租與供電節點仍未落地，設備採購節奏會被延後，這些資訊仍需要與長約條款一併核對。</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="162" customHeight="1">
+          <t>對精密電源與量測設備業者而言，這批核准案代表可追蹤的工程與接電需求管線，而不是立即可認列的設備銷售。下一步要核對的是分期上線節點、電網可用餘裕與實際租戶導入速度。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="146" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
           <t>02</t>
@@ -739,7 +739,7 @@
               <color rgb="0014322B"/>
               <sz val="13"/>
             </rPr>
-            <t xml:space="preserve">神雲新廠與擴線計畫再度公開，產能時間表仍未一併定義
+            <t xml:space="preserve">馬來半島資料中心用電需求估 2030 年達 8,391MW，Johor 比重過半
 </t>
           </r>
           <r>
@@ -748,16 +748,16 @@
               <color rgb="003B4A44"/>
               <sz val="11"/>
             </rPr>
-            <t>神雲公布約 126.2 億元台灣投資案，涵蓋楊梅新廠、竹南與林口擴線，但公司未併同披露各站點的設備到位日期與開產驗收標準。這類案件仍以設備採購與擴產規劃為主，而非當前已出貨或已上線產能。投資案涵蓋新廠與原有產線擴大，對應伺服器、AI 相關組裝與電源技術的擴充需求。從供應鏈觀點，這代表先前產線、機櫃與高密度供電需求仍在擴張，而不是單一一個量產站點已完全落地。公司未披露每個廠區的建廠工期、設備交期或新產能電力負載需求，因此不能將公布的投資額直接等同於近期期望出貨量。這些資訊會在後續公告中納入，唯目前仍須以計畫與驗收條件分開理解。投資額、土地與工廠計畫已公開，但尚未公布實際開工日、設備到位日期與單站點產能目標，因此目前只能確認資本計畫與擴產方向。地點：台灣桃園楊梅、新竹竹南、桃園林口；以廠區計畫為主。</t>
+            <t>10/21 追蹤報導顯示，馬來半島資料中心在 2030 年的用電需求估達 8,391MW，且 Johor 占比超過一半。這是需求估算，不是現況負載；對供應鏈的實際影響仍取決於電力系統升級、並網審批與機房分期投運。資料中心需求往往先反映在申請容量與併網規劃，其後才轉化為可用 IT 負載。若區域電網升級、變電站擴容與備援建設進度不同步，估算需求不會立即轉成可交付容量。本則聚焦區域用電需求與地理分布，不重複前日對單一企業合約覆蓋率或機房交付節點的敘述。重點從單案營運數字轉為系統性電力壓力與配套建設。尚未取得完整公開清單可逐案比對各園區實際接電與上架時間，因此目前僅能把 8,391MW 視為需求規模指標。地點：馬來西亞半島（Johor 為主要集中區）。</t>
           </r>
         </is>
       </c>
       <c r="C4" s="6" t="n">
-        <v>46314</v>
+        <v>46316</v>
       </c>
       <c r="D4" s="10" t="inlineStr">
         <is>
-          <t>對伺服器與電源供應鏈業者而言，這類投資案更多反映中長期產線準備，而不是立即性的出貨增量。關鍵要看設備交期、工廠通電和產線驗收，否則會把計畫性擴張誤判為已達成產能。</t>
+          <t>對精密電源與量測設備業者而言，8,391MW 代表的是潛在設計容量，不是當期可認列市場。要評估接單窗口，仍需同步追蹤變電節點、並網核准與客戶分期上架是否一致。</t>
         </is>
       </c>
     </row>
@@ -776,7 +776,7 @@
               <color rgb="0014322B"/>
               <sz val="13"/>
             </rPr>
-            <t xml:space="preserve">宸鴻與力成的封裝設備與玻璃基板驗證，仍以試產與客戶認證為核心
+            <t xml:space="preserve">越南電子製造擴產訊號升溫，十億美元級投資意向待落地
 </t>
           </r>
           <r>
@@ -785,16 +785,16 @@
               <color rgb="003B4A44"/>
               <sz val="11"/>
             </rPr>
-            <t>宸鴻提出兩年 60 億元 TGV 規劃，力成則披露近期設備採購與封裝驗證節點。這些動作都強調驗證、規模擴張與適配客戶流程，尚無法視為量產落地，因為設備採購、試產與客戶驗證是不同的節點。TGV、玻璃基板與分析設備屬先進封裝與高密度電源供應鏈的關鍵工具，關係到基板載具、熱管理與客戶驗證。這些案子都還是以試產、設備安裝與線體驗證為主，並不等同量產契約的落地。區域設備採購與工廠規劃固然代表業者持續投入，但投資額要與實務量產、良率改善和客戶通過率分開看待。對供應鏈而言，技術能力還須在實際樣品與客戶驗證中確認。目前公開資料未提供完整良率、設備利用率與轉換班別資料，因此仍不能將規劃與試產直接界定成商業量產起點。地點：台灣；涉及封裝、玻璃基板與設備服務的測試與工程節點。</t>
+            <t>10/21 匯整的供應鏈報導提到，越南電子與半導體測試鏈條持續出現十億美元等級投資意向，包括台系與韓系廠商的擴產規劃。現階段多為公告與媒體揭露，對產能與就業的實際影響仍須等正式核准、施工與設備進場時程。越南擴產若落地，會連動封測、電力系統、治具、自動化與周邊材料需求。對台灣與東南亞鏈條而言，重點不是單一新聞數字，而是是否形成連續的專案核准與設備導入節奏。本則改為越南電子製造與測試鏈條的跨國投資觀察，避免重複前日馬來西亞機房與台灣單一企業投資題材。分析重點落在區域產能遷移與擴廠執行條件。目前公開內容未完整揭露各案最終核准條件、施工里程碑與量產節點，因此仍不能把投資意向直接視為短期新增可用產能。地點：越南北部電子製造走廊（含測試與封測相關基地）。</t>
           </r>
         </is>
       </c>
       <c r="C5" s="9" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="D5" s="10" t="inlineStr">
         <is>
-          <t>對供應鏈與封裝設備業者而言，這類投資案的意義在於技術與驗證能力的建立，而不是已經到達量產節點。要確認的關鍵是良率、交貨與客戶驗證是否持續向前，不是僅看資本支出總額。</t>
+          <t>對精密電源與量測設備業者而言，越南擴產訊號的價值在於中期設備需求可見度提升，但時點仍受核准與施工牽引。現階段應先追蹤接電、測試線建置與客戶導入順序，不宜把意向金額直接轉成短期營收推估。</t>
         </is>
       </c>
     </row>
